--- a/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-small_satellite_buildings.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-small_satellite_buildings.xlsx
@@ -591,56 +591,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n">
-        <v>44.48400282859802</v>
+        <v>53.33050775527954</v>
       </c>
       <c r="D2" t="n">
         <v>0.6800000071525574</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0369391964846535</v>
+        <v>0.0408052231439134</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8427557945251465</v>
+        <v>0.8572753667831421</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8161134719848633</v>
+        <v>0.8439821600914001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8165237903594971</v>
+        <v>0.8446773290634155</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8170020580291748</v>
+        <v>0.8385026454925537</v>
       </c>
       <c r="J2" t="n">
-        <v>0.032907485961914</v>
+        <v>0.030190547928214</v>
       </c>
       <c r="K2" t="n">
-        <v>39.02065062522888</v>
+        <v>24.89928817749023</v>
       </c>
       <c r="L2" t="n">
-        <v>1.675788640975952</v>
+        <v>1.694292306900024</v>
       </c>
       <c r="M2" t="n">
-        <v>7.924580574035645</v>
+        <v>8.345993995666504</v>
       </c>
       <c r="N2" t="n">
-        <v>8.512500762939453</v>
+        <v>8.83409595489502</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1396490534146627</v>
+        <v>0.141191025575002</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6603817145029703</v>
+        <v>0.6954994996388754</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7093750635782877</v>
+        <v>0.7361746629079183</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-120327</t>
+          <t>20250720-044853</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -665,22 +665,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -690,10 +690,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -715,53 +715,53 @@
         <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>44.84239292144776</v>
+        <v>45.77901411056519</v>
       </c>
       <c r="D3" t="n">
         <v>0.6800000071525574</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0398472047067786</v>
+        <v>0.032601622668536</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8599501848220825</v>
+        <v>0.8540570139884949</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8384997248649597</v>
+        <v>0.8290161490440369</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8391055464744568</v>
+        <v>0.8297570943832397</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8343053460121155</v>
+        <v>0.825420618057251</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0300567150115966</v>
+        <v>0.0313494987785816</v>
       </c>
       <c r="K3" t="n">
-        <v>24.69768810272217</v>
+        <v>25.13433146476746</v>
       </c>
       <c r="L3" t="n">
-        <v>1.647673845291138</v>
+        <v>1.677394866943359</v>
       </c>
       <c r="M3" t="n">
-        <v>8.019488573074341</v>
+        <v>8.321346282958984</v>
       </c>
       <c r="N3" t="n">
-        <v>9.661404371261597</v>
+        <v>8.687252521514893</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1373061537742614</v>
+        <v>0.1397829055786132</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6682907144228617</v>
+        <v>0.6934455235799154</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8051170309384664</v>
+        <v>0.7239377101262411</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-120604</t>
+          <t>20250720-045128</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -786,22 +786,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -811,10 +811,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -836,53 +836,53 @@
         <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>44.26540398597717</v>
+        <v>46.42796587944031</v>
       </c>
       <c r="D4" t="n">
         <v>0.6800000071525574</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0341608736075852</v>
+        <v>0.0336821841468151</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8539232015609741</v>
+        <v>0.8561002016067505</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8321036696434021</v>
+        <v>0.8355381488800049</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8326053619384766</v>
+        <v>0.8359988331794739</v>
       </c>
       <c r="I4" t="n">
-        <v>0.831881046295166</v>
+        <v>0.8366516828536987</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0299558639526367</v>
+        <v>0.0355552844703197</v>
       </c>
       <c r="K4" t="n">
-        <v>24.28987574577332</v>
+        <v>24.97275137901306</v>
       </c>
       <c r="L4" t="n">
-        <v>1.613939046859741</v>
+        <v>1.706556797027588</v>
       </c>
       <c r="M4" t="n">
-        <v>8.247854232788086</v>
+        <v>8.201456308364868</v>
       </c>
       <c r="N4" t="n">
-        <v>8.302978515625</v>
+        <v>8.490008592605591</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1344949205716451</v>
+        <v>0.1422130664189656</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6873211860656738</v>
+        <v>0.683454692363739</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6919148763020834</v>
+        <v>0.7075007160504659</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-120829</t>
+          <t>20250720-045355</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -907,22 +907,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -932,10 +932,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -954,56 +954,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" t="n">
-        <v>46.11246705055237</v>
+        <v>45.2402400970459</v>
       </c>
       <c r="D5" t="n">
         <v>0.6800000071525574</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0380227464991501</v>
+        <v>0.0355226341144818</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8573770523071289</v>
+        <v>0.8544526100158691</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8357317447662354</v>
+        <v>0.8156734108924866</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8358910083770752</v>
+        <v>0.8165510296821594</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8285311460494995</v>
+        <v>0.8178302049636841</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0299309100955724</v>
+        <v>0.0323874950408935</v>
       </c>
       <c r="K5" t="n">
-        <v>24.90734934806824</v>
+        <v>25.26343488693237</v>
       </c>
       <c r="L5" t="n">
-        <v>1.626113176345825</v>
+        <v>1.654618501663208</v>
       </c>
       <c r="M5" t="n">
-        <v>8.755773782730103</v>
+        <v>8.527137279510498</v>
       </c>
       <c r="N5" t="n">
-        <v>8.311381101608276</v>
+        <v>8.744796514511108</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1355094313621521</v>
+        <v>0.1378848751386006</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7296478152275085</v>
+        <v>0.7105947732925415</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6926150918006897</v>
+        <v>0.7287330428759257</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-121052</t>
+          <t>20250720-045622</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1028,22 +1028,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1053,10 +1053,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1075,56 +1075,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" t="n">
-        <v>46.88901352882385</v>
+        <v>45.99605941772461</v>
       </c>
       <c r="D6" t="n">
         <v>0.6800000071525574</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0380157178315596</v>
+        <v>0.0322482935398032</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8532112240791321</v>
+        <v>0.8581544160842896</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8300409317016602</v>
+        <v>0.8412575721740723</v>
       </c>
       <c r="H6" t="n">
-        <v>0.830092191696167</v>
+        <v>0.8419471383094788</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8267995119094849</v>
+        <v>0.8380681872367859</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0300972461700439</v>
+        <v>0.0305508766323328</v>
       </c>
       <c r="K6" t="n">
-        <v>24.76501679420471</v>
+        <v>24.89605164527893</v>
       </c>
       <c r="L6" t="n">
-        <v>1.657937526702881</v>
+        <v>1.700667142868042</v>
       </c>
       <c r="M6" t="n">
-        <v>8.133947134017944</v>
+        <v>8.425635814666748</v>
       </c>
       <c r="N6" t="n">
-        <v>8.514225721359253</v>
+        <v>8.877121448516846</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1381614605585734</v>
+        <v>0.1417222619056701</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6778289278348287</v>
+        <v>0.7021363178888956</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7095188101132711</v>
+        <v>0.7397601207097372</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-121318</t>
+          <t>20250720-045849</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1174,10 +1174,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1362,56 +1362,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n">
-        <v>58.4463746547699</v>
+        <v>70.81404757499695</v>
       </c>
       <c r="D2" t="n">
         <v>2.319999933242798</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1485383953703076</v>
+        <v>0.1516414978964761</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8509253859519958</v>
+        <v>0.8607847690582275</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7761330604553223</v>
+        <v>0.8515223264694214</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7763904929161072</v>
+        <v>0.8510557413101196</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7828185558319092</v>
+        <v>0.8433056473731995</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0494204349815845</v>
+        <v>0.0531787872314453</v>
       </c>
       <c r="K2" t="n">
-        <v>40.80281400680542</v>
+        <v>42.69347715377808</v>
       </c>
       <c r="L2" t="n">
-        <v>1.808377027511597</v>
+        <v>2.288635969161988</v>
       </c>
       <c r="M2" t="n">
-        <v>9.009013175964355</v>
+        <v>9.444538354873655</v>
       </c>
       <c r="N2" t="n">
-        <v>16.63257145881653</v>
+        <v>11.05604076385498</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1506980856259664</v>
+        <v>0.1907196640968322</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7507510979970297</v>
+        <v>0.7870448629061381</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.386047621568044</v>
+        <v>0.9213367303212484</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-121226</t>
+          <t>20250718-083827</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1436,22 +1436,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1461,10 +1461,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1486,53 +1486,53 @@
         <v>39</v>
       </c>
       <c r="C3" t="n">
-        <v>61.6515941619873</v>
+        <v>63.39610362052917</v>
       </c>
       <c r="D3" t="n">
         <v>2.319999933242798</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1464584236725782</v>
+        <v>0.1503766847726625</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8591724038124084</v>
+        <v>0.8711426258087158</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8078433275222778</v>
+        <v>0.8338133096694946</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8080379962921143</v>
+        <v>0.8349463939666748</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8038926720619202</v>
+        <v>0.8408216238021851</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0780640468001365</v>
+        <v>0.057007472962141</v>
       </c>
       <c r="K3" t="n">
-        <v>37.48442602157593</v>
+        <v>36.90922427177429</v>
       </c>
       <c r="L3" t="n">
-        <v>1.925181865692139</v>
+        <v>1.971269845962524</v>
       </c>
       <c r="M3" t="n">
-        <v>8.604876756668091</v>
+        <v>9.114150524139404</v>
       </c>
       <c r="N3" t="n">
-        <v>13.13926672935486</v>
+        <v>11.16223978996277</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1604318221410115</v>
+        <v>0.1642724871635437</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7170730630556742</v>
+        <v>0.7595125436782837</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.094938894112905</v>
+        <v>0.930186649163564</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-121528</t>
+          <t>20250718-084156</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1557,22 +1557,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1582,10 +1582,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1604,56 +1604,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>60.74794888496399</v>
+        <v>60.23064398765564</v>
       </c>
       <c r="D4" t="n">
         <v>2.319999933242798</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1494385886650818</v>
+        <v>0.1496947378312286</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8524571657180786</v>
+        <v>0.8615410327911377</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8286067247390747</v>
+        <v>0.8089884519577026</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8290191888809204</v>
+        <v>0.8107537031173706</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8354951143264771</v>
+        <v>0.8222408294677734</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0591434650123119</v>
+        <v>0.0624016113579273</v>
       </c>
       <c r="K4" t="n">
-        <v>38.98132967948914</v>
+        <v>36.75308871269226</v>
       </c>
       <c r="L4" t="n">
-        <v>2.197239637374878</v>
+        <v>1.976129531860352</v>
       </c>
       <c r="M4" t="n">
-        <v>9.139499664306641</v>
+        <v>9.250256299972534</v>
       </c>
       <c r="N4" t="n">
-        <v>13.16953158378601</v>
+        <v>11.53423523902893</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1831033031145731</v>
+        <v>0.1646774609883626</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7616249720255533</v>
+        <v>0.7708546916643778</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.097460965315501</v>
+        <v>0.9611862699190776</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-121826</t>
+          <t>20250718-084456</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1678,22 +1678,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1703,10 +1703,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1725,56 +1725,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" t="n">
-        <v>58.51619553565979</v>
+        <v>63.66376924514771</v>
       </c>
       <c r="D5" t="n">
         <v>2.319999933242798</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1392745675617142</v>
+        <v>0.1552441192743105</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8763184547424316</v>
+        <v>0.8711238503456116</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8370049595832825</v>
+        <v>0.8392326831817627</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8369514942169189</v>
+        <v>0.839320957660675</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8432666063308716</v>
+        <v>0.8459859490394592</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0488888435065746</v>
+        <v>0.07059582322835919</v>
       </c>
       <c r="K5" t="n">
-        <v>36.17771100997925</v>
+        <v>42.52671933174133</v>
       </c>
       <c r="L5" t="n">
-        <v>1.868027448654175</v>
+        <v>1.976281881332397</v>
       </c>
       <c r="M5" t="n">
-        <v>8.582837581634521</v>
+        <v>9.857060194015505</v>
       </c>
       <c r="N5" t="n">
-        <v>10.78439927101135</v>
+        <v>10.84203338623047</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1556689540545145</v>
+        <v>0.1646901567776998</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7152364651362101</v>
+        <v>0.8214216828346252</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.898699939250946</v>
+        <v>0.9035027821858724</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-122146</t>
+          <t>20250718-084753</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1799,22 +1799,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1824,10 +1824,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1849,53 +1849,53 @@
         <v>39</v>
       </c>
       <c r="C6" t="n">
-        <v>62.13273453712464</v>
+        <v>63.23689007759094</v>
       </c>
       <c r="D6" t="n">
         <v>2.319999933242798</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1467169259603206</v>
+        <v>0.1537541303879175</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8525433540344238</v>
+        <v>0.8622909784317017</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8291288614273071</v>
+        <v>0.824368953704834</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8286193609237671</v>
+        <v>0.825928807258606</v>
       </c>
       <c r="I6" t="n">
-        <v>0.830744743347168</v>
+        <v>0.8332541584968567</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0551288910210132</v>
+        <v>0.0512460879981517</v>
       </c>
       <c r="K6" t="n">
-        <v>35.81575441360474</v>
+        <v>37.05184364318848</v>
       </c>
       <c r="L6" t="n">
-        <v>1.893025636672974</v>
+        <v>1.933812856674194</v>
       </c>
       <c r="M6" t="n">
-        <v>8.603979349136353</v>
+        <v>8.886614799499512</v>
       </c>
       <c r="N6" t="n">
-        <v>11.25443601608276</v>
+        <v>11.15610980987549</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1577521363894144</v>
+        <v>0.1611510713895162</v>
       </c>
       <c r="P6" t="n">
-        <v>0.716998279094696</v>
+        <v>0.740551233291626</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.937869668006897</v>
+        <v>0.929675817489624</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-122438</t>
+          <t>20250718-085114</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1945,10 +1945,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2133,56 +2133,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" t="n">
-        <v>55.05343222618103</v>
+        <v>57.88979578018188</v>
       </c>
       <c r="D2" t="n">
         <v>1.070000052452087</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1190710589289664</v>
+        <v>0.1261740770095433</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7928495407104492</v>
+        <v>0.827042281627655</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7890778779983521</v>
+        <v>0.8241700530052185</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7883132100105286</v>
+        <v>0.8231304883956909</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7085945606231689</v>
+        <v>0.7898250818252563</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0429550819098949</v>
+        <v>0.0500832386314868</v>
       </c>
       <c r="K2" t="n">
-        <v>36.02383041381836</v>
+        <v>37.26102781295776</v>
       </c>
       <c r="L2" t="n">
-        <v>1.710491895675659</v>
+        <v>1.806296348571777</v>
       </c>
       <c r="M2" t="n">
-        <v>15.4521951675415</v>
+        <v>14.61559748649597</v>
       </c>
       <c r="N2" t="n">
-        <v>17.11180305480957</v>
+        <v>17.32555460929871</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1425409913063049</v>
+        <v>0.1505246957143148</v>
       </c>
       <c r="P2" t="n">
-        <v>1.287682930628459</v>
+        <v>1.217966457207998</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.425983587900798</v>
+        <v>1.443796217441559</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-151715</t>
+          <t>20250718-144627</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2207,22 +2207,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -2232,10 +2232,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2254,56 +2254,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C3" t="n">
-        <v>54.49142789840698</v>
+        <v>72.43295979499817</v>
       </c>
       <c r="D3" t="n">
         <v>1.070000052452087</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1191048480962451</v>
+        <v>0.1251463286426602</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8074173927307129</v>
+        <v>0.8494150042533875</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8142910003662109</v>
+        <v>0.8236355781555176</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8130199909210205</v>
+        <v>0.8238968849182129</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6965764164924622</v>
+        <v>0.7790928483009338</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0427455119788646</v>
+        <v>0.0436864681541919</v>
       </c>
       <c r="K3" t="n">
-        <v>36.21814322471619</v>
+        <v>37.64288592338562</v>
       </c>
       <c r="L3" t="n">
-        <v>1.725385904312134</v>
+        <v>1.826390981674194</v>
       </c>
       <c r="M3" t="n">
-        <v>14.4503870010376</v>
+        <v>14.76119542121887</v>
       </c>
       <c r="N3" t="n">
-        <v>15.84299969673157</v>
+        <v>17.81202292442322</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1437821586926778</v>
+        <v>0.1521992484728495</v>
       </c>
       <c r="P3" t="n">
-        <v>1.204198916753133</v>
+        <v>1.230099618434906</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.320249974727631</v>
+        <v>1.484335243701935</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-152029</t>
+          <t>20250718-144947</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -2328,22 +2328,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -2353,10 +2353,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2375,56 +2375,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>55.36034274101257</v>
+        <v>59.12995004653931</v>
       </c>
       <c r="D4" t="n">
         <v>1.070000052452087</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1156230068912631</v>
+        <v>0.1255117975748501</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8017034530639648</v>
+        <v>0.8339531421661377</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7713786363601685</v>
+        <v>0.7815902233123779</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7705882787704468</v>
+        <v>0.781079888343811</v>
       </c>
       <c r="I4" t="n">
-        <v>0.700969934463501</v>
+        <v>0.7094683051109314</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0476028136909008</v>
+        <v>0.066338300704956</v>
       </c>
       <c r="K4" t="n">
-        <v>36.36356115341187</v>
+        <v>36.6881206035614</v>
       </c>
       <c r="L4" t="n">
-        <v>1.729260921478272</v>
+        <v>1.875254154205322</v>
       </c>
       <c r="M4" t="n">
-        <v>14.32476282119751</v>
+        <v>14.66602659225464</v>
       </c>
       <c r="N4" t="n">
-        <v>16.91542267799377</v>
+        <v>17.34963774681091</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1441050767898559</v>
+        <v>0.1562711795171102</v>
       </c>
       <c r="P4" t="n">
-        <v>1.193730235099792</v>
+        <v>1.222168882687886</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.409618556499481</v>
+        <v>1.445803145567576</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-152340</t>
+          <t>20250718-145323</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -2474,10 +2474,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2496,56 +2496,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" t="n">
-        <v>54.42300820350647</v>
+        <v>58.36229658126831</v>
       </c>
       <c r="D5" t="n">
         <v>1.070000052452087</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1192278230660839</v>
+        <v>0.1247306487117057</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8098635673522949</v>
+        <v>0.8190593123435974</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7963277101516724</v>
+        <v>0.787318229675293</v>
       </c>
       <c r="H5" t="n">
-        <v>0.79473876953125</v>
+        <v>0.7873162627220154</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6780455112457275</v>
+        <v>0.6630169153213501</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0669780597090721</v>
+        <v>0.051368873566389</v>
       </c>
       <c r="K5" t="n">
-        <v>35.95449781417847</v>
+        <v>37.24516940116882</v>
       </c>
       <c r="L5" t="n">
-        <v>1.807288408279419</v>
+        <v>1.855566501617432</v>
       </c>
       <c r="M5" t="n">
-        <v>14.00179982185364</v>
+        <v>14.64119553565979</v>
       </c>
       <c r="N5" t="n">
-        <v>16.6218855381012</v>
+        <v>16.66643619537354</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1506073673566182</v>
+        <v>0.1546305418014526</v>
       </c>
       <c r="P5" t="n">
-        <v>1.166816651821136</v>
+        <v>1.220099627971649</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.3851571281751</v>
+        <v>1.388869682947795</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-152654</t>
+          <t>20250718-145643</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2570,22 +2570,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -2595,10 +2595,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2620,53 +2620,53 @@
         <v>39</v>
       </c>
       <c r="C6" t="n">
-        <v>55.92297291755676</v>
+        <v>58.83424043655396</v>
       </c>
       <c r="D6" t="n">
         <v>1.070000052452087</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1161389463605024</v>
+        <v>0.1257229808431404</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8292241096496582</v>
+        <v>0.8292301893234253</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8154610395431519</v>
+        <v>0.8159539103507996</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8140977621078491</v>
+        <v>0.8157695531845093</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6646929979324341</v>
+        <v>0.783775269985199</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04925974085927</v>
+        <v>0.0513761043548584</v>
       </c>
       <c r="K6" t="n">
-        <v>36.68802404403687</v>
+        <v>37.17136979103088</v>
       </c>
       <c r="L6" t="n">
-        <v>1.715394973754883</v>
+        <v>2.127710103988647</v>
       </c>
       <c r="M6" t="n">
-        <v>15.54896950721741</v>
+        <v>15.94384407997131</v>
       </c>
       <c r="N6" t="n">
-        <v>16.84777355194092</v>
+        <v>17.76153182983398</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1429495811462402</v>
+        <v>0.1773091753323873</v>
       </c>
       <c r="P6" t="n">
-        <v>1.295747458934784</v>
+        <v>1.328653673330943</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.40398112932841</v>
+        <v>1.480127652486165</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-153006</t>
+          <t>20250718-150003</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2691,22 +2691,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2716,10 +2716,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2904,56 +2904,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>79.77248549461365</v>
+        <v>103.6335046291351</v>
       </c>
       <c r="D2" t="n">
         <v>8.539999961853027</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3101007946227726</v>
+        <v>0.3123508041002312</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8778858184814453</v>
+        <v>0.8893385529518127</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8351443409919739</v>
+        <v>0.8644102811813354</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8348159790039062</v>
+        <v>0.8638218641281128</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6702209115028381</v>
+        <v>0.7170205116271973</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1058802604675293</v>
+        <v>0.093891941010952</v>
       </c>
       <c r="K2" t="n">
-        <v>163.3615341186523</v>
+        <v>174.1426711082458</v>
       </c>
       <c r="L2" t="n">
-        <v>2.886933326721191</v>
+        <v>2.960570573806763</v>
       </c>
       <c r="M2" t="n">
-        <v>11.40045857429504</v>
+        <v>12.09376454353332</v>
       </c>
       <c r="N2" t="n">
-        <v>17.94744729995728</v>
+        <v>18.63466238975525</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2405777772267659</v>
+        <v>0.2467142144838968</v>
       </c>
       <c r="P2" t="n">
-        <v>0.950038214524587</v>
+        <v>1.00781371196111</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.495620608329773</v>
+        <v>1.552888532479604</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-182819</t>
+          <t>20250718-204319</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2978,22 +2978,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3003,10 +3003,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3025,56 +3025,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C3" t="n">
-        <v>79.51708889007568</v>
+        <v>85.4157862663269</v>
       </c>
       <c r="D3" t="n">
         <v>8.539999961853027</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3062807235278581</v>
+        <v>0.3169814730301881</v>
       </c>
       <c r="F3" t="n">
-        <v>0.813797652721405</v>
+        <v>0.8901442289352417</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8268940448760986</v>
+        <v>0.8584970831871033</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8279168605804443</v>
+        <v>0.8568189144134521</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6716759204864502</v>
+        <v>0.6871411204338074</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0949289798736572</v>
+        <v>0.0937377586960792</v>
       </c>
       <c r="K3" t="n">
-        <v>170.4131810665131</v>
+        <v>167.9704766273499</v>
       </c>
       <c r="L3" t="n">
-        <v>2.508256435394287</v>
+        <v>2.91585659980774</v>
       </c>
       <c r="M3" t="n">
-        <v>11.88696622848511</v>
+        <v>12.15971899032593</v>
       </c>
       <c r="N3" t="n">
-        <v>17.99540972709656</v>
+        <v>18.91114211082458</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2090213696161905</v>
+        <v>0.2429880499839782</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9905805190404257</v>
+        <v>1.013309915860494</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.499617477258046</v>
+        <v>1.575928509235382</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-183438</t>
+          <t>20250718-205010</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3099,22 +3099,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3124,10 +3124,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3146,56 +3146,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>80.55207705497742</v>
+        <v>84.19134855270386</v>
       </c>
       <c r="D4" t="n">
         <v>8.539999961853027</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3077258538258703</v>
+        <v>0.3155334247992589</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8734914064407349</v>
+        <v>0.8867286443710327</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8118646144866943</v>
+        <v>0.8486341834068298</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8117214441299438</v>
+        <v>0.8473412394523621</v>
       </c>
       <c r="I4" t="n">
-        <v>0.639204204082489</v>
+        <v>0.6845172643661499</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0912915840744972</v>
+        <v>0.09210840612649911</v>
       </c>
       <c r="K4" t="n">
-        <v>161.9479269981384</v>
+        <v>168.9990158081055</v>
       </c>
       <c r="L4" t="n">
-        <v>2.827247142791748</v>
+        <v>2.932449340820312</v>
       </c>
       <c r="M4" t="n">
-        <v>11.32895946502686</v>
+        <v>11.68815183639526</v>
       </c>
       <c r="N4" t="n">
-        <v>18.64184951782227</v>
+        <v>18.78640460968018</v>
       </c>
       <c r="O4" t="n">
-        <v>0.235603928565979</v>
+        <v>0.2443707784016927</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9440799554189048</v>
+        <v>0.9740126530329386</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.553487459818522</v>
+        <v>1.565533717473348</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-184057</t>
+          <t>20250718-205638</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3220,22 +3220,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -3245,10 +3245,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3267,56 +3267,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C5" t="n">
-        <v>80.84405732154846</v>
+        <v>105.4236218929291</v>
       </c>
       <c r="D5" t="n">
         <v>8.539999961853027</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3128583211647837</v>
+        <v>0.3182035532532906</v>
       </c>
       <c r="F5" t="n">
-        <v>0.864327073097229</v>
+        <v>0.8955326080322266</v>
       </c>
       <c r="G5" t="n">
-        <v>0.809284508228302</v>
+        <v>0.8812040090560913</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8098936080932617</v>
+        <v>0.8808962106704712</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7078901529312134</v>
+        <v>0.6502006649971008</v>
       </c>
       <c r="J5" t="n">
-        <v>0.09118429571390151</v>
+        <v>0.0936048850417137</v>
       </c>
       <c r="K5" t="n">
-        <v>161.97980260849</v>
+        <v>167.5131456851959</v>
       </c>
       <c r="L5" t="n">
-        <v>2.837936639785767</v>
+        <v>3.017603635787964</v>
       </c>
       <c r="M5" t="n">
-        <v>11.41458606719971</v>
+        <v>11.65580773353577</v>
       </c>
       <c r="N5" t="n">
-        <v>18.29704928398132</v>
+        <v>19.01870894432068</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2364947199821472</v>
+        <v>0.251466969648997</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9512155055999756</v>
+        <v>0.9713173111279806</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.524754106998444</v>
+        <v>1.584892412026723</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-184655</t>
+          <t>20250718-210310</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3341,22 +3341,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -3366,10 +3366,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3388,56 +3388,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n">
-        <v>79.13896346092224</v>
+        <v>84.89679551124573</v>
       </c>
       <c r="D6" t="n">
         <v>8.539999961853027</v>
       </c>
       <c r="E6" t="n">
-        <v>0.303603271120473</v>
+        <v>0.314804189480268</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8329822421073914</v>
+        <v>0.8819471001625061</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8414843082427979</v>
+        <v>0.8510732054710388</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8428081870079041</v>
+        <v>0.8508644104003906</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7171733379364014</v>
+        <v>0.7169907093048096</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1128105297684669</v>
+        <v>0.09393429756164549</v>
       </c>
       <c r="K6" t="n">
-        <v>170.8426764011383</v>
+        <v>167.6987321376801</v>
       </c>
       <c r="L6" t="n">
-        <v>2.61843466758728</v>
+        <v>2.888361215591431</v>
       </c>
       <c r="M6" t="n">
-        <v>11.72298979759216</v>
+        <v>11.89771747589111</v>
       </c>
       <c r="N6" t="n">
-        <v>18.18737745285035</v>
+        <v>18.80446672439575</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2182028889656067</v>
+        <v>0.2406967679659525</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9769158164660136</v>
+        <v>0.9914764563242594</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.515614787737529</v>
+        <v>1.567038893699646</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-185313</t>
+          <t>20250718-211002</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -3462,22 +3462,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3487,10 +3487,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3675,56 +3675,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>68.94504404067993</v>
+        <v>90.84266138076782</v>
       </c>
       <c r="D2" t="n">
         <v>7.130000114440918</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1821034593801749</v>
+        <v>0.1828777297418944</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7213417291641235</v>
+        <v>0.7809159755706787</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6338633894920349</v>
+        <v>0.7362121939659119</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6355839967727661</v>
+        <v>0.7354651689529419</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5339934229850769</v>
+        <v>0.6510187983512878</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0678637847304344</v>
+        <v>0.0669395104050636</v>
       </c>
       <c r="K2" t="n">
-        <v>65.07484102249146</v>
+        <v>32.00518774986267</v>
       </c>
       <c r="L2" t="n">
-        <v>2.556710004806519</v>
+        <v>2.348804712295532</v>
       </c>
       <c r="M2" t="n">
-        <v>8.846779823303223</v>
+        <v>8.979927778244019</v>
       </c>
       <c r="N2" t="n">
-        <v>11.28639078140259</v>
+        <v>11.23652982711792</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2130591670672098</v>
+        <v>0.1957337260246276</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7372316519419352</v>
+        <v>0.7483273148536682</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9405325651168824</v>
+        <v>0.93637748559316</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-045807</t>
+          <t>20250719-132056</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3749,22 +3749,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3774,10 +3774,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3796,56 +3796,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>70.25731158256531</v>
+        <v>69.11720705032349</v>
       </c>
       <c r="D3" t="n">
         <v>7.130000114440918</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1849749653767316</v>
+        <v>0.18323925215947</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7558876872062683</v>
+        <v>0.7243491411209106</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7304404973983765</v>
+        <v>0.6519601345062256</v>
       </c>
       <c r="H3" t="n">
-        <v>0.731145977973938</v>
+        <v>0.6503967642784119</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6713816523551941</v>
+        <v>0.5093042254447937</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0720317363739013</v>
+        <v>0.0686705112457275</v>
       </c>
       <c r="K3" t="n">
-        <v>36.30265164375305</v>
+        <v>36.89620161056519</v>
       </c>
       <c r="L3" t="n">
-        <v>2.555129766464233</v>
+        <v>2.459386587142944</v>
       </c>
       <c r="M3" t="n">
-        <v>8.99436354637146</v>
+        <v>9.021799564361572</v>
       </c>
       <c r="N3" t="n">
-        <v>11.04719161987305</v>
+        <v>11.261155128479</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2129274805386861</v>
+        <v>0.204948882261912</v>
       </c>
       <c r="P3" t="n">
-        <v>0.749530295530955</v>
+        <v>0.7518166303634644</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9205993016560872</v>
+        <v>0.938429594039917</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-050150</t>
+          <t>20250719-132436</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3870,22 +3870,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3895,10 +3895,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3920,53 +3920,53 @@
         <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>69.36497521400452</v>
+        <v>68.78782081604004</v>
       </c>
       <c r="D4" t="n">
         <v>7.130000114440918</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1811950159700293</v>
+        <v>0.182879293827634</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7583370208740234</v>
+        <v>0.7238684892654419</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7243468761444092</v>
+        <v>0.6339197754859924</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7238482236862183</v>
+        <v>0.6323339939117432</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6691585183143616</v>
+        <v>0.5208148956298828</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07019885629415509</v>
+        <v>0.0701947212219238</v>
       </c>
       <c r="K4" t="n">
-        <v>41.85931968688965</v>
+        <v>36.74715828895569</v>
       </c>
       <c r="L4" t="n">
-        <v>2.569790363311768</v>
+        <v>2.635044574737549</v>
       </c>
       <c r="M4" t="n">
-        <v>9.065636873245239</v>
+        <v>9.213802099227903</v>
       </c>
       <c r="N4" t="n">
-        <v>11.03466844558716</v>
+        <v>11.57372999191284</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2141491969426473</v>
+        <v>0.2195870478947957</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7554697394371033</v>
+        <v>0.7678168416023254</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9195557037989298</v>
+        <v>0.9644774993260702</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-050506</t>
+          <t>20250719-132753</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3991,22 +3991,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4016,10 +4016,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4041,53 +4041,53 @@
         <v>38</v>
       </c>
       <c r="C5" t="n">
-        <v>69.35008716583252</v>
+        <v>69.54836535453796</v>
       </c>
       <c r="D5" t="n">
         <v>7.130000114440918</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1823176800420409</v>
+        <v>0.1829555764010077</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7377897500991821</v>
+        <v>0.7530513405799866</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6578450798988342</v>
+        <v>0.6367878913879395</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6586018204689026</v>
+        <v>0.6357095837593079</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6242287755012512</v>
+        <v>0.5665007829666138</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0717998370528221</v>
+        <v>0.0680538788437843</v>
       </c>
       <c r="K5" t="n">
-        <v>43.61038398742676</v>
+        <v>36.98244023323059</v>
       </c>
       <c r="L5" t="n">
-        <v>2.576673746109009</v>
+        <v>2.459142446517944</v>
       </c>
       <c r="M5" t="n">
-        <v>9.318831443786619</v>
+        <v>9.323043823242188</v>
       </c>
       <c r="N5" t="n">
-        <v>11.80699491500854</v>
+        <v>11.21340012550354</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2147228121757507</v>
+        <v>0.2049285372098287</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7765692869822184</v>
+        <v>0.7769203186035156</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9839162429173788</v>
+        <v>0.9344500104586284</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-050827</t>
+          <t>20250719-133111</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4112,22 +4112,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4137,10 +4137,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4159,56 +4159,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C6" t="n">
-        <v>69.31399011611938</v>
+        <v>125.2582366466522</v>
       </c>
       <c r="D6" t="n">
         <v>7.130000114440918</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1811498713336492</v>
+        <v>0.1825007517700609</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7609391212463379</v>
+        <v>0.8500016927719116</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7021552920341492</v>
+        <v>0.8027631044387817</v>
       </c>
       <c r="H6" t="n">
-        <v>0.70201176404953</v>
+        <v>0.8020639419555664</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5500736236572266</v>
+        <v>0.7430918216705322</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0742749348282814</v>
+        <v>0.0673023089766502</v>
       </c>
       <c r="K6" t="n">
-        <v>40.68543410301208</v>
+        <v>36.38558173179626</v>
       </c>
       <c r="L6" t="n">
-        <v>2.603981494903564</v>
+        <v>2.399601459503174</v>
       </c>
       <c r="M6" t="n">
-        <v>8.959609746932983</v>
+        <v>9.01856255531311</v>
       </c>
       <c r="N6" t="n">
-        <v>11.26871490478516</v>
+        <v>11.52878141403198</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2169984579086303</v>
+        <v>0.1999667882919311</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7466341455777487</v>
+        <v>0.7515468796094259</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9390595753987632</v>
+        <v>0.9607317845026652</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-051151</t>
+          <t>20250719-133429</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4233,22 +4233,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -4258,10 +4258,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4446,56 +4446,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" t="n">
-        <v>54.44600486755371</v>
+        <v>59.24077439308167</v>
       </c>
       <c r="D2" t="n">
-        <v>4.210000038146973</v>
+        <v>4.21999979019165</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1100970841944217</v>
+        <v>0.1118148423922367</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7359176874160767</v>
+        <v>0.7681484818458557</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7099908590316772</v>
+        <v>0.7512894868850708</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7072083950042725</v>
+        <v>0.7502082586288452</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7068642377853394</v>
+        <v>0.7369145750999451</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0456271171569824</v>
+        <v>0.0497600249946117</v>
       </c>
       <c r="K2" t="n">
-        <v>31.35041785240173</v>
+        <v>18.96874928474426</v>
       </c>
       <c r="L2" t="n">
-        <v>1.651794910430908</v>
+        <v>2.097837924957275</v>
       </c>
       <c r="M2" t="n">
-        <v>7.502048492431641</v>
+        <v>8.119319200515747</v>
       </c>
       <c r="N2" t="n">
-        <v>15.79010844230652</v>
+        <v>8.736038446426392</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1376495758692423</v>
+        <v>0.1748198270797729</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6251707077026367</v>
+        <v>0.6766099333763123</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.31584237019221</v>
+        <v>0.728003203868866</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-075616</t>
+          <t>20250719-194832</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4520,22 +4520,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4545,10 +4545,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4570,53 +4570,53 @@
         <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>53.96010851860046</v>
+        <v>55.85191965103149</v>
       </c>
       <c r="D3" t="n">
         <v>4.210000038146973</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1097369733217515</v>
+        <v>0.1117729132896975</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7038265466690063</v>
+        <v>0.7514011859893799</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6604971289634705</v>
+        <v>0.7132983803749084</v>
       </c>
       <c r="H3" t="n">
-        <v>0.661197304725647</v>
+        <v>0.7112311124801636</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6878877878189087</v>
+        <v>0.6838502883911133</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0444246120750904</v>
+        <v>0.0430121421813964</v>
       </c>
       <c r="K3" t="n">
-        <v>19.04469585418701</v>
+        <v>19.12200570106506</v>
       </c>
       <c r="L3" t="n">
-        <v>1.919580221176148</v>
+        <v>2.206352233886719</v>
       </c>
       <c r="M3" t="n">
-        <v>7.559602737426758</v>
+        <v>7.993302345275879</v>
       </c>
       <c r="N3" t="n">
-        <v>8.858714580535889</v>
+        <v>8.797682523727417</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1599650184313456</v>
+        <v>0.1838626861572265</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6299668947855631</v>
+        <v>0.6661085287729899</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7382262150446574</v>
+        <v>0.733140210310618</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-075911</t>
+          <t>20250719-195114</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4666,10 +4666,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4688,56 +4688,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>54.90106773376465</v>
+        <v>59.81967973709106</v>
       </c>
       <c r="D4" t="n">
-        <v>4.210000038146973</v>
+        <v>4.21999979019165</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1102989108154647</v>
+        <v>0.1111697720793576</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7804012298583984</v>
+        <v>0.7511184811592102</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7370525002479553</v>
+        <v>0.7183569073677063</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7366585731506348</v>
+        <v>0.7162857055664062</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7380159497261047</v>
+        <v>0.7217757701873779</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0436575412750244</v>
+        <v>0.04284493252635</v>
       </c>
       <c r="K4" t="n">
-        <v>23.955650806427</v>
+        <v>19.35852742195129</v>
       </c>
       <c r="L4" t="n">
-        <v>2.079252243041992</v>
+        <v>2.178910732269287</v>
       </c>
       <c r="M4" t="n">
-        <v>7.399751663208008</v>
+        <v>7.79816722869873</v>
       </c>
       <c r="N4" t="n">
-        <v>8.611599206924438</v>
+        <v>9.175762414932253</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1732710202534993</v>
+        <v>0.1815758943557739</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6166459719340006</v>
+        <v>0.6498472690582275</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7176332672437032</v>
+        <v>0.7646468679110209</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-080146</t>
+          <t>20250719-195353</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4762,22 +4762,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4787,10 +4787,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4809,56 +4809,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" t="n">
-        <v>54.82090401649475</v>
+        <v>60.10404920578003</v>
       </c>
       <c r="D5" t="n">
         <v>4.210000038146973</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1094107367098331</v>
+        <v>0.1107305786930597</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7497196197509766</v>
+        <v>0.7617562413215637</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7423045635223389</v>
+        <v>0.7353466749191284</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7390825152397156</v>
+        <v>0.7347970008850098</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7427194714546204</v>
+        <v>0.7206995487213135</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0424363613128662</v>
+        <v>0.0521230697631835</v>
       </c>
       <c r="K5" t="n">
-        <v>23.87763905525208</v>
+        <v>24.73036885261536</v>
       </c>
       <c r="L5" t="n">
-        <v>2.057440757751465</v>
+        <v>2.168038606643677</v>
       </c>
       <c r="M5" t="n">
-        <v>7.501101493835449</v>
+        <v>7.887514352798462</v>
       </c>
       <c r="N5" t="n">
-        <v>8.688004493713379</v>
+        <v>8.831470727920532</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1714533964792887</v>
+        <v>0.180669883886973</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6250917911529541</v>
+        <v>0.6572928627332052</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7240003744761149</v>
+        <v>0.7359558939933777</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-080420</t>
+          <t>20250719-195637</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4908,10 +4908,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4930,56 +4930,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n">
-        <v>54.86357283592224</v>
+        <v>59.64116168022156</v>
       </c>
       <c r="D6" t="n">
-        <v>4.210000038146973</v>
+        <v>4.21999979019165</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1106250037096048</v>
+        <v>0.1116938491662342</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7522996664047241</v>
+        <v>0.746173620223999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7158933877944946</v>
+        <v>0.6793244481086731</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7190818786621094</v>
+        <v>0.6782305836677551</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7200503349304199</v>
+        <v>0.6679348349571228</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0425729751586914</v>
+        <v>0.0446321181952953</v>
       </c>
       <c r="K6" t="n">
-        <v>24.18456029891968</v>
+        <v>18.79312014579773</v>
       </c>
       <c r="L6" t="n">
-        <v>1.994631052017212</v>
+        <v>2.021730661392212</v>
       </c>
       <c r="M6" t="n">
-        <v>7.495749711990356</v>
+        <v>7.796379327774048</v>
       </c>
       <c r="N6" t="n">
-        <v>16.80363082885742</v>
+        <v>8.811955451965332</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1662192543347676</v>
+        <v>0.1684775551160176</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6246458093325297</v>
+        <v>0.649698277314504</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.400302569071452</v>
+        <v>0.734329620997111</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-080656</t>
+          <t>20250719-195920</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5004,22 +5004,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5029,10 +5029,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5220,53 +5220,53 @@
         <v>38</v>
       </c>
       <c r="C2" t="n">
-        <v>51.63856315612793</v>
+        <v>53.89302229881287</v>
       </c>
       <c r="D2" t="n">
         <v>2.809999942779541</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0994527359542093</v>
+        <v>0.1023805098314034</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7390766143798828</v>
+        <v>0.7516684532165527</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7433539628982544</v>
+        <v>0.6885724067687988</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7429099082946777</v>
+        <v>0.6868134737014771</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7440580129623413</v>
+        <v>0.6873812675476074</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0373461246490478</v>
+        <v>0.0362508296966552</v>
       </c>
       <c r="K2" t="n">
-        <v>22.83445835113525</v>
+        <v>23.18435645103454</v>
       </c>
       <c r="L2" t="n">
-        <v>1.893768310546875</v>
+        <v>1.974176168441772</v>
       </c>
       <c r="M2" t="n">
-        <v>7.973830223083496</v>
+        <v>8.444583892822266</v>
       </c>
       <c r="N2" t="n">
-        <v>9.71990442276001</v>
+        <v>9.512596607208252</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1578140258789062</v>
+        <v>0.164514680703481</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6644858519236246</v>
+        <v>0.7037153244018555</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8099920352300009</v>
+        <v>0.792716383934021</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-100653</t>
+          <t>20250720-001118</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5291,22 +5291,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5316,10 +5316,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5338,56 +5338,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C3" t="n">
-        <v>51.38945651054382</v>
+        <v>56.31847667694092</v>
       </c>
       <c r="D3" t="n">
         <v>2.809999942779541</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0981701341898817</v>
+        <v>0.1005713154490177</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7647661566734314</v>
+        <v>0.7357177734375</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6894753575325012</v>
+        <v>0.7032692432403564</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6877779960632324</v>
+        <v>0.7044950723648071</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6815063953399658</v>
+        <v>0.6435073018074036</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0345261096954345</v>
+        <v>0.0376570224761962</v>
       </c>
       <c r="K3" t="n">
-        <v>23.23409128189087</v>
+        <v>23.57219123840332</v>
       </c>
       <c r="L3" t="n">
-        <v>1.900110721588135</v>
+        <v>1.734437942504883</v>
       </c>
       <c r="M3" t="n">
-        <v>7.971848249435425</v>
+        <v>8.343053102493286</v>
       </c>
       <c r="N3" t="n">
-        <v>9.713529825210571</v>
+        <v>9.455350875854492</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1583425601323445</v>
+        <v>0.1445364952087402</v>
       </c>
       <c r="P3" t="n">
-        <v>0.664320687452952</v>
+        <v>0.6952544252077738</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8094608187675476</v>
+        <v>0.7879459063212076</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-100925</t>
+          <t>20250720-001355</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5412,22 +5412,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5437,10 +5437,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5459,56 +5459,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>51.14395785331726</v>
+        <v>55.25925087928772</v>
       </c>
       <c r="D4" t="n">
         <v>2.809999942779541</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1000709167044413</v>
+        <v>0.1012061956601264</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7101240158081055</v>
+        <v>0.7418212890625</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6498705148696899</v>
+        <v>0.6979333162307739</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6460835933685303</v>
+        <v>0.6966990232467651</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6437472701072693</v>
+        <v>0.6961019039154053</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0347225666046142</v>
+        <v>0.0380349159240722</v>
       </c>
       <c r="K4" t="n">
-        <v>22.82705092430115</v>
+        <v>23.7610125541687</v>
       </c>
       <c r="L4" t="n">
-        <v>1.619522094726562</v>
+        <v>1.697547435760498</v>
       </c>
       <c r="M4" t="n">
-        <v>8.021223068237305</v>
+        <v>8.333701848983765</v>
       </c>
       <c r="N4" t="n">
-        <v>8.914948701858521</v>
+        <v>9.802629947662354</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1349601745605468</v>
+        <v>0.1414622863133748</v>
       </c>
       <c r="P4" t="n">
-        <v>0.668435255686442</v>
+        <v>0.6944751540819804</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7429123918215433</v>
+        <v>0.8168858289718628</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-101158</t>
+          <t>20250720-001635</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5533,22 +5533,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5558,10 +5558,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5583,53 +5583,53 @@
         <v>39</v>
       </c>
       <c r="C5" t="n">
-        <v>54.02354192733765</v>
+        <v>56.64010643959045</v>
       </c>
       <c r="D5" t="n">
         <v>2.809999942779541</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0991505902165021</v>
+        <v>0.1026273853121659</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7453098297119141</v>
+        <v>0.7426595687866211</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6736220121383667</v>
+        <v>0.7420934438705444</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6721647381782532</v>
+        <v>0.742026686668396</v>
       </c>
       <c r="I5" t="n">
-        <v>0.669706404209137</v>
+        <v>0.7433436512947083</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0345038585364818</v>
+        <v>0.0515377521514892</v>
       </c>
       <c r="K5" t="n">
-        <v>23.00641131401062</v>
+        <v>23.80171418190002</v>
       </c>
       <c r="L5" t="n">
-        <v>1.872992515563965</v>
+        <v>1.757633447647095</v>
       </c>
       <c r="M5" t="n">
-        <v>7.940639734268188</v>
+        <v>8.330028295516968</v>
       </c>
       <c r="N5" t="n">
-        <v>9.221455335617064</v>
+        <v>10.04406976699829</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1560827096303304</v>
+        <v>0.1464694539705912</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6617199778556824</v>
+        <v>0.6941690246264139</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7684546113014221</v>
+        <v>0.8370058139165243</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-101415</t>
+          <t>20250720-001914</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5679,10 +5679,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5701,56 +5701,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n">
-        <v>51.61722207069397</v>
+        <v>54.78823280334473</v>
       </c>
       <c r="D6" t="n">
         <v>2.809999942779541</v>
       </c>
       <c r="E6" t="n">
-        <v>0.098535882603181</v>
+        <v>0.100705923178257</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7260786294937134</v>
+        <v>0.7479730248451233</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6598176956176758</v>
+        <v>0.697075366973877</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6573313474655151</v>
+        <v>0.6970201730728149</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6332811713218689</v>
+        <v>0.6878833770751953</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0345923900604248</v>
+        <v>0.0358688831329345</v>
       </c>
       <c r="K6" t="n">
-        <v>17.25484275817871</v>
+        <v>23.9289939403534</v>
       </c>
       <c r="L6" t="n">
-        <v>1.942240476608276</v>
+        <v>1.646290063858032</v>
       </c>
       <c r="M6" t="n">
-        <v>7.698657274246216</v>
+        <v>8.574026823043823</v>
       </c>
       <c r="N6" t="n">
-        <v>8.778907060623169</v>
+        <v>9.460681438446043</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1618533730506897</v>
+        <v>0.137190838654836</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6415547728538513</v>
+        <v>0.714502235253652</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.731575588385264</v>
+        <v>0.7883901198705038</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-101649</t>
+          <t>20250720-002155</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5775,22 +5775,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5800,10 +5800,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>

--- a/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-small_satellite_buildings.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-small_satellite_buildings.xlsx
@@ -591,56 +591,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C2" t="n">
-        <v>53.33050775527954</v>
+        <v>74.80808568000793</v>
       </c>
       <c r="D2" t="n">
         <v>0.6800000071525574</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0408052231439134</v>
+        <v>0.0383261607494204</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8572753667831421</v>
+        <v>0.8577752113342285</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8439821600914001</v>
+        <v>0.84245765209198</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8446773290634155</v>
+        <v>0.8431133031845093</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8385026454925537</v>
+        <v>0.8356770277023315</v>
       </c>
       <c r="J2" t="n">
-        <v>0.030190547928214</v>
+        <v>0.0329355411231517</v>
       </c>
       <c r="K2" t="n">
-        <v>24.89928817749023</v>
+        <v>25.01879668235779</v>
       </c>
       <c r="L2" t="n">
-        <v>1.694292306900024</v>
+        <v>1.752976179122925</v>
       </c>
       <c r="M2" t="n">
-        <v>8.345993995666504</v>
+        <v>8.360609769821167</v>
       </c>
       <c r="N2" t="n">
-        <v>8.83409595489502</v>
+        <v>8.813008546829224</v>
       </c>
       <c r="O2" t="n">
-        <v>0.141191025575002</v>
+        <v>0.1460813482602437</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6954994996388754</v>
+        <v>0.6967174808184305</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7361746629079183</v>
+        <v>0.7344173789024353</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250720-044853</t>
+          <t>20250723-152831</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -712,56 +712,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="C3" t="n">
-        <v>45.77901411056519</v>
+        <v>99.11187291145325</v>
       </c>
       <c r="D3" t="n">
         <v>0.6800000071525574</v>
       </c>
       <c r="E3" t="n">
-        <v>0.032601622668536</v>
+        <v>0.0320885135747846</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8540570139884949</v>
+        <v>0.8592833876609802</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8290161490440369</v>
+        <v>0.8396365642547607</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8297570943832397</v>
+        <v>0.8411097526550293</v>
       </c>
       <c r="I3" t="n">
-        <v>0.825420618057251</v>
+        <v>0.8339641094207764</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0313494987785816</v>
+        <v>0.0383776016533374</v>
       </c>
       <c r="K3" t="n">
-        <v>25.13433146476746</v>
+        <v>25.1085569858551</v>
       </c>
       <c r="L3" t="n">
-        <v>1.677394866943359</v>
+        <v>1.70079231262207</v>
       </c>
       <c r="M3" t="n">
-        <v>8.321346282958984</v>
+        <v>8.303502082824707</v>
       </c>
       <c r="N3" t="n">
-        <v>8.687252521514893</v>
+        <v>8.761977434158325</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1397829055786132</v>
+        <v>0.1417326927185058</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6934455235799154</v>
+        <v>0.691958506902059</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7239377101262411</v>
+        <v>0.7301647861798605</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250720-045128</t>
+          <t>20250723-153127</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -833,56 +833,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="C4" t="n">
-        <v>46.42796587944031</v>
+        <v>100.9734284877777</v>
       </c>
       <c r="D4" t="n">
         <v>0.6800000071525574</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0336821841468151</v>
+        <v>0.0353526024754797</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8561002016067505</v>
+        <v>0.8606855273246765</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8355381488800049</v>
+        <v>0.8454681634902954</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8359988331794739</v>
+        <v>0.8465082049369812</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8366516828536987</v>
+        <v>0.8408435583114624</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0355552844703197</v>
+        <v>0.0300587806850671</v>
       </c>
       <c r="K4" t="n">
-        <v>24.97275137901306</v>
+        <v>24.82117795944214</v>
       </c>
       <c r="L4" t="n">
-        <v>1.706556797027588</v>
+        <v>1.680408716201782</v>
       </c>
       <c r="M4" t="n">
-        <v>8.201456308364868</v>
+        <v>8.767746448516846</v>
       </c>
       <c r="N4" t="n">
-        <v>8.490008592605591</v>
+        <v>9.178208351135254</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1422130664189656</v>
+        <v>0.1400340596834818</v>
       </c>
       <c r="P4" t="n">
-        <v>0.683454692363739</v>
+        <v>0.7306455373764038</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7075007160504659</v>
+        <v>0.7648506959279379</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250720-045355</t>
+          <t>20250723-153448</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -954,56 +954,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="C5" t="n">
-        <v>45.2402400970459</v>
+        <v>95.12226557731628</v>
       </c>
       <c r="D5" t="n">
         <v>0.6800000071525574</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0355226341144818</v>
+        <v>0.0362074227693179</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8544526100158691</v>
+        <v>0.8608050346374512</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8156734108924866</v>
+        <v>0.8480172157287598</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8165510296821594</v>
+        <v>0.8477881550788879</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8178302049636841</v>
+        <v>0.8391352891921997</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0323874950408935</v>
+        <v>0.0307350158691406</v>
       </c>
       <c r="K5" t="n">
-        <v>25.26343488693237</v>
+        <v>24.68467354774475</v>
       </c>
       <c r="L5" t="n">
-        <v>1.654618501663208</v>
+        <v>1.713854312896728</v>
       </c>
       <c r="M5" t="n">
-        <v>8.527137279510498</v>
+        <v>8.326754331588745</v>
       </c>
       <c r="N5" t="n">
-        <v>8.744796514511108</v>
+        <v>9.112346172332764</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1378848751386006</v>
+        <v>0.142821192741394</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7105947732925415</v>
+        <v>0.6938961942990621</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7287330428759257</v>
+        <v>0.7593621810277303</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250720-045622</t>
+          <t>20250723-153810</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1075,56 +1075,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="C6" t="n">
-        <v>45.99605941772461</v>
+        <v>109.0175092220306</v>
       </c>
       <c r="D6" t="n">
         <v>0.6800000071525574</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0322482935398032</v>
+        <v>0.0429053169457201</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8581544160842896</v>
+        <v>0.8595687747001648</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8412575721740723</v>
+        <v>0.8546885251998901</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8419471383094788</v>
+        <v>0.8550331592559814</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8380681872367859</v>
+        <v>0.8503966331481934</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0305508766323328</v>
+        <v>0.0346475429832935</v>
       </c>
       <c r="K6" t="n">
-        <v>24.89605164527893</v>
+        <v>24.93831014633179</v>
       </c>
       <c r="L6" t="n">
-        <v>1.700667142868042</v>
+        <v>1.72480320930481</v>
       </c>
       <c r="M6" t="n">
-        <v>8.425635814666748</v>
+        <v>8.785160541534424</v>
       </c>
       <c r="N6" t="n">
-        <v>8.877121448516846</v>
+        <v>8.47144627571106</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1417222619056701</v>
+        <v>0.1437336007754008</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7021363178888956</v>
+        <v>0.7320967117945353</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7397601207097372</v>
+        <v>0.705953856309255</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250720-045849</t>
+          <t>20250723-154127</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1362,56 +1362,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="C2" t="n">
-        <v>70.81404757499695</v>
+        <v>208.6979577541352</v>
       </c>
       <c r="D2" t="n">
         <v>2.319999933242798</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1516414978964761</v>
+        <v>0.1524088469555051</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8607847690582275</v>
+        <v>0.901561677455902</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8515223264694214</v>
+        <v>0.8642361164093018</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8510557413101196</v>
+        <v>0.8640050888061523</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8433056473731995</v>
+        <v>0.8606364727020264</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0531787872314453</v>
+        <v>0.0569788627326488</v>
       </c>
       <c r="K2" t="n">
-        <v>42.69347715377808</v>
+        <v>37.00520491600037</v>
       </c>
       <c r="L2" t="n">
-        <v>2.288635969161988</v>
+        <v>1.995927572250366</v>
       </c>
       <c r="M2" t="n">
-        <v>9.444538354873655</v>
+        <v>8.914632797241211</v>
       </c>
       <c r="N2" t="n">
-        <v>11.05604076385498</v>
+        <v>11.32828760147095</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1907196640968322</v>
+        <v>0.1663272976875305</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7870448629061381</v>
+        <v>0.7428860664367676</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9213367303212484</v>
+        <v>0.9440239667892456</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-083827</t>
+          <t>20250721-140348</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1483,56 +1483,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="C3" t="n">
-        <v>63.39610362052917</v>
+        <v>149.3733425140381</v>
       </c>
       <c r="D3" t="n">
         <v>2.319999933242798</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1503766847726625</v>
+        <v>0.1532915382072179</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8711426258087158</v>
+        <v>0.9043737649917604</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8338133096694946</v>
+        <v>0.8725216388702393</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8349463939666748</v>
+        <v>0.8711053729057312</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8408216238021851</v>
+        <v>0.8635766506195068</v>
       </c>
       <c r="J3" t="n">
-        <v>0.057007472962141</v>
+        <v>0.0590104274451732</v>
       </c>
       <c r="K3" t="n">
-        <v>36.90922427177429</v>
+        <v>36.82287406921387</v>
       </c>
       <c r="L3" t="n">
-        <v>1.971269845962524</v>
+        <v>1.990398168563843</v>
       </c>
       <c r="M3" t="n">
-        <v>9.114150524139404</v>
+        <v>9.016847848892212</v>
       </c>
       <c r="N3" t="n">
-        <v>11.16223978996277</v>
+        <v>11.45731830596924</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1642724871635437</v>
+        <v>0.1658665140469869</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7595125436782837</v>
+        <v>0.7514039874076843</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.930186649163564</v>
+        <v>0.9547765254974364</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250718-084156</t>
+          <t>20250721-140914</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1604,56 +1604,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="C4" t="n">
-        <v>60.23064398765564</v>
+        <v>151.1391172409058</v>
       </c>
       <c r="D4" t="n">
         <v>2.319999933242798</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1496947378312286</v>
+        <v>0.1502728281599102</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8615410327911377</v>
+        <v>0.8999437093734741</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8089884519577026</v>
+        <v>0.8402208685874939</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8107537031173706</v>
+        <v>0.8398571014404297</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8222408294677734</v>
+        <v>0.8424184322357178</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0624016113579273</v>
+        <v>0.0603396110236644</v>
       </c>
       <c r="K4" t="n">
-        <v>36.75308871269226</v>
+        <v>42.9530713558197</v>
       </c>
       <c r="L4" t="n">
-        <v>1.976129531860352</v>
+        <v>2.027093887329102</v>
       </c>
       <c r="M4" t="n">
-        <v>9.250256299972534</v>
+        <v>9.249086856842039</v>
       </c>
       <c r="N4" t="n">
-        <v>11.53423523902893</v>
+        <v>10.67689156532288</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1646774609883626</v>
+        <v>0.1689244906107584</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7708546916643778</v>
+        <v>0.77075723807017</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9611862699190776</v>
+        <v>0.8897409637769064</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250718-084456</t>
+          <t>20250721-141340</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1725,56 +1725,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="C5" t="n">
-        <v>63.66376924514771</v>
+        <v>158.7757511138916</v>
       </c>
       <c r="D5" t="n">
         <v>2.319999933242798</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1552441192743105</v>
+        <v>0.1546338130361758</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8711238503456116</v>
+        <v>0.8956277370452881</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8392326831817627</v>
+        <v>0.8705593943595886</v>
       </c>
       <c r="H5" t="n">
-        <v>0.839320957660675</v>
+        <v>0.8694720268249512</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8459859490394592</v>
+        <v>0.871561586856842</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07059582322835919</v>
+        <v>0.0531535148620605</v>
       </c>
       <c r="K5" t="n">
-        <v>42.52671933174133</v>
+        <v>36.80417227745056</v>
       </c>
       <c r="L5" t="n">
-        <v>1.976281881332397</v>
+        <v>2.006289482116699</v>
       </c>
       <c r="M5" t="n">
-        <v>9.857060194015505</v>
+        <v>9.065513849258425</v>
       </c>
       <c r="N5" t="n">
-        <v>10.84203338623047</v>
+        <v>11.30146551132202</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1646901567776998</v>
+        <v>0.1671907901763916</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8214216828346252</v>
+        <v>0.7554594874382019</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9035027821858724</v>
+        <v>0.9417887926101683</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250718-084753</t>
+          <t>20250721-141828</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1846,56 +1846,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="C6" t="n">
-        <v>63.23689007759094</v>
+        <v>222.7031853199005</v>
       </c>
       <c r="D6" t="n">
         <v>2.319999933242798</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1537541303879175</v>
+        <v>0.1515398635060194</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8622909784317017</v>
+        <v>0.9040467739105223</v>
       </c>
       <c r="G6" t="n">
-        <v>0.824368953704834</v>
+        <v>0.8576801419258118</v>
       </c>
       <c r="H6" t="n">
-        <v>0.825928807258606</v>
+        <v>0.85650634765625</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8332541584968567</v>
+        <v>0.8601425886154175</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0512460879981517</v>
+        <v>0.0523541755974292</v>
       </c>
       <c r="K6" t="n">
-        <v>37.05184364318848</v>
+        <v>42.70887327194214</v>
       </c>
       <c r="L6" t="n">
-        <v>1.933812856674194</v>
+        <v>2.277887105941772</v>
       </c>
       <c r="M6" t="n">
-        <v>8.886614799499512</v>
+        <v>9.878930807113647</v>
       </c>
       <c r="N6" t="n">
-        <v>11.15610980987549</v>
+        <v>11.12184190750122</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1611510713895162</v>
+        <v>0.1898239254951477</v>
       </c>
       <c r="P6" t="n">
-        <v>0.740551233291626</v>
+        <v>0.8232442339261373</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.929675817489624</v>
+        <v>0.9268201589584352</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250718-085114</t>
+          <t>20250721-142324</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2133,56 +2133,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="C2" t="n">
-        <v>57.88979578018188</v>
+        <v>132.7460825443268</v>
       </c>
       <c r="D2" t="n">
         <v>1.070000052452087</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1261740770095433</v>
+        <v>0.1265259550765473</v>
       </c>
       <c r="F2" t="n">
-        <v>0.827042281627655</v>
+        <v>0.8457583785057068</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8241700530052185</v>
+        <v>0.8259563446044922</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8231304883956909</v>
+        <v>0.826033353805542</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7898250818252563</v>
+        <v>0.6649738550186157</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0500832386314868</v>
+        <v>0.0436023063957691</v>
       </c>
       <c r="K2" t="n">
-        <v>37.26102781295776</v>
+        <v>36.71222758293152</v>
       </c>
       <c r="L2" t="n">
-        <v>1.806296348571777</v>
+        <v>1.828110218048096</v>
       </c>
       <c r="M2" t="n">
-        <v>14.61559748649597</v>
+        <v>14.88038945198059</v>
       </c>
       <c r="N2" t="n">
-        <v>17.32555460929871</v>
+        <v>17.79606175422668</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1505246957143148</v>
+        <v>0.1523425181706746</v>
       </c>
       <c r="P2" t="n">
-        <v>1.217966457207998</v>
+        <v>1.240032454331716</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.443796217441559</v>
+        <v>1.483005146185557</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-144627</t>
+          <t>20250721-205200</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2254,56 +2254,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="C3" t="n">
-        <v>72.43295979499817</v>
+        <v>139.5463864803314</v>
       </c>
       <c r="D3" t="n">
         <v>1.070000052452087</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1251463286426602</v>
+        <v>0.1272473834229237</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8494150042533875</v>
+        <v>0.8657903075218201</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8236355781555176</v>
+        <v>0.8559426069259644</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8238968849182129</v>
+        <v>0.8557881116867065</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7790928483009338</v>
+        <v>0.7801245450973511</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0436864681541919</v>
+        <v>0.0505283661186695</v>
       </c>
       <c r="K3" t="n">
-        <v>37.64288592338562</v>
+        <v>37.18479871749878</v>
       </c>
       <c r="L3" t="n">
-        <v>1.826390981674194</v>
+        <v>2.113373994827271</v>
       </c>
       <c r="M3" t="n">
-        <v>14.76119542121887</v>
+        <v>15.01231932640076</v>
       </c>
       <c r="N3" t="n">
-        <v>17.81202292442322</v>
+        <v>18.05377197265625</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1521992484728495</v>
+        <v>0.1761144995689392</v>
       </c>
       <c r="P3" t="n">
-        <v>1.230099618434906</v>
+        <v>1.251026610533396</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.484335243701935</v>
+        <v>1.504480997721354</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250718-144947</t>
+          <t>20250721-205636</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -2375,56 +2375,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="C4" t="n">
-        <v>59.12995004653931</v>
+        <v>160.5879213809967</v>
       </c>
       <c r="D4" t="n">
         <v>1.070000052452087</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1255117975748501</v>
+        <v>0.1256692185344403</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8339531421661377</v>
+        <v>0.8599619269371033</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7815902233123779</v>
+        <v>0.8417726755142212</v>
       </c>
       <c r="H4" t="n">
-        <v>0.781079888343811</v>
+        <v>0.8425379991531372</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7094683051109314</v>
+        <v>0.7845524549484253</v>
       </c>
       <c r="J4" t="n">
-        <v>0.066338300704956</v>
+        <v>0.0578741244971752</v>
       </c>
       <c r="K4" t="n">
-        <v>36.6881206035614</v>
+        <v>37.26603198051453</v>
       </c>
       <c r="L4" t="n">
-        <v>1.875254154205322</v>
+        <v>1.917437553405761</v>
       </c>
       <c r="M4" t="n">
-        <v>14.66602659225464</v>
+        <v>14.5958034992218</v>
       </c>
       <c r="N4" t="n">
-        <v>17.34963774681091</v>
+        <v>18.04596281051636</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1562711795171102</v>
+        <v>0.1597864627838134</v>
       </c>
       <c r="P4" t="n">
-        <v>1.222168882687886</v>
+        <v>1.216316958268483</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.445803145567576</v>
+        <v>1.503830234209696</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250718-145323</t>
+          <t>20250721-210118</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2496,56 +2496,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="C5" t="n">
-        <v>58.36229658126831</v>
+        <v>113.0993649959564</v>
       </c>
       <c r="D5" t="n">
         <v>1.070000052452087</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1247306487117057</v>
+        <v>0.1260912198620506</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8190593123435974</v>
+        <v>0.8586635589599609</v>
       </c>
       <c r="G5" t="n">
-        <v>0.787318229675293</v>
+        <v>0.8357688784599304</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7873162627220154</v>
+        <v>0.8351633548736572</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6630169153213501</v>
+        <v>0.7663773894309998</v>
       </c>
       <c r="J5" t="n">
-        <v>0.051368873566389</v>
+        <v>0.0424607582390308</v>
       </c>
       <c r="K5" t="n">
-        <v>37.24516940116882</v>
+        <v>37.11205625534058</v>
       </c>
       <c r="L5" t="n">
-        <v>1.855566501617432</v>
+        <v>1.840330600738525</v>
       </c>
       <c r="M5" t="n">
-        <v>14.64119553565979</v>
+        <v>14.76332497596741</v>
       </c>
       <c r="N5" t="n">
-        <v>16.66643619537354</v>
+        <v>17.31413078308105</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1546305418014526</v>
+        <v>0.1533608833948771</v>
       </c>
       <c r="P5" t="n">
-        <v>1.220099627971649</v>
+        <v>1.230277081330617</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.388869682947795</v>
+        <v>1.442844231923421</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250718-145643</t>
+          <t>20250721-210622</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2617,56 +2617,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="C6" t="n">
-        <v>58.83424043655396</v>
+        <v>125.5802562236786</v>
       </c>
       <c r="D6" t="n">
         <v>1.070000052452087</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1257229808431404</v>
+        <v>0.1256040093604098</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8292301893234253</v>
+        <v>0.8400912880897522</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8159539103507996</v>
+        <v>0.8342288136482239</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8157695531845093</v>
+        <v>0.8344106078147888</v>
       </c>
       <c r="I6" t="n">
-        <v>0.783775269985199</v>
+        <v>0.761089563369751</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0513761043548584</v>
+        <v>0.0425093956291675</v>
       </c>
       <c r="K6" t="n">
-        <v>37.17136979103088</v>
+        <v>37.19631719589233</v>
       </c>
       <c r="L6" t="n">
-        <v>2.127710103988647</v>
+        <v>1.848402500152588</v>
       </c>
       <c r="M6" t="n">
-        <v>15.94384407997131</v>
+        <v>14.82744741439819</v>
       </c>
       <c r="N6" t="n">
-        <v>17.76153182983398</v>
+        <v>17.87253856658936</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1773091753323873</v>
+        <v>0.1540335416793823</v>
       </c>
       <c r="P6" t="n">
-        <v>1.328653673330943</v>
+        <v>1.235620617866516</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.480127652486165</v>
+        <v>1.489378213882446</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250718-150003</t>
+          <t>20250721-211037</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2904,56 +2904,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="C2" t="n">
-        <v>103.6335046291351</v>
+        <v>261.5326647758484</v>
       </c>
       <c r="D2" t="n">
         <v>8.539999961853027</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3123508041002312</v>
+        <v>0.315391236728476</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8893385529518127</v>
+        <v>0.9063730239868164</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8644102811813354</v>
+        <v>0.8796483278274536</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8638218641281128</v>
+        <v>0.8791429400444031</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7170205116271973</v>
+        <v>0.6999325752258301</v>
       </c>
       <c r="J2" t="n">
-        <v>0.093891941010952</v>
+        <v>0.1045284271240234</v>
       </c>
       <c r="K2" t="n">
-        <v>174.1426711082458</v>
+        <v>168.6147494316101</v>
       </c>
       <c r="L2" t="n">
-        <v>2.960570573806763</v>
+        <v>3.095174312591553</v>
       </c>
       <c r="M2" t="n">
-        <v>12.09376454353332</v>
+        <v>12.35848808288574</v>
       </c>
       <c r="N2" t="n">
-        <v>18.63466238975525</v>
+        <v>19.33093738555908</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2467142144838968</v>
+        <v>0.2579311927159627</v>
       </c>
       <c r="P2" t="n">
-        <v>1.00781371196111</v>
+        <v>1.029874006907145</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.552888532479604</v>
+        <v>1.61091144879659</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-204319</t>
+          <t>20250722-033305</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3025,56 +3025,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="C3" t="n">
-        <v>85.4157862663269</v>
+        <v>212.6919798851013</v>
       </c>
       <c r="D3" t="n">
         <v>8.539999961853027</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3169814730301881</v>
+        <v>0.319253371312068</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8901442289352417</v>
+        <v>0.9139981269836426</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8584970831871033</v>
+        <v>0.8722993135452271</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8568189144134521</v>
+        <v>0.8712524175643921</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6871411204338074</v>
+        <v>0.7671104073524475</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0937377586960792</v>
+        <v>0.0953001976013183</v>
       </c>
       <c r="K3" t="n">
-        <v>167.9704766273499</v>
+        <v>167.4569158554077</v>
       </c>
       <c r="L3" t="n">
-        <v>2.91585659980774</v>
+        <v>3.009018898010254</v>
       </c>
       <c r="M3" t="n">
-        <v>12.15971899032593</v>
+        <v>11.70602107048035</v>
       </c>
       <c r="N3" t="n">
-        <v>18.91114211082458</v>
+        <v>18.89093780517578</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2429880499839782</v>
+        <v>0.2507515748341878</v>
       </c>
       <c r="P3" t="n">
-        <v>1.013309915860494</v>
+        <v>0.9755017558733622</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.575928509235382</v>
+        <v>1.574244817097982</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250718-205010</t>
+          <t>20250722-034210</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3146,56 +3146,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C4" t="n">
-        <v>84.19134855270386</v>
+        <v>144.519017457962</v>
       </c>
       <c r="D4" t="n">
         <v>8.539999961853027</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3155334247992589</v>
+        <v>0.3157889933689781</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8867286443710327</v>
+        <v>0.8940797448158264</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8486341834068298</v>
+        <v>0.8545218706130981</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8473412394523621</v>
+        <v>0.8557085990905762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6845172643661499</v>
+        <v>0.570764422416687</v>
       </c>
       <c r="J4" t="n">
-        <v>0.09210840612649911</v>
+        <v>0.0984679833054542</v>
       </c>
       <c r="K4" t="n">
-        <v>168.9990158081055</v>
+        <v>168.5043115615845</v>
       </c>
       <c r="L4" t="n">
-        <v>2.932449340820312</v>
+        <v>2.929129838943481</v>
       </c>
       <c r="M4" t="n">
-        <v>11.68815183639526</v>
+        <v>11.8143355846405</v>
       </c>
       <c r="N4" t="n">
-        <v>18.78640460968018</v>
+        <v>18.82900428771973</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2443707784016927</v>
+        <v>0.2440941532452901</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9740126530329386</v>
+        <v>0.9845279653867086</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.565533717473348</v>
+        <v>1.56908369064331</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250718-205638</t>
+          <t>20250722-035050</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3267,56 +3267,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="C5" t="n">
-        <v>105.4236218929291</v>
+        <v>233.3036754131317</v>
       </c>
       <c r="D5" t="n">
         <v>8.539999961853027</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3182035532532906</v>
+        <v>0.3130788348223033</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8955326080322266</v>
+        <v>0.9184639453887939</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8812040090560913</v>
+        <v>0.8879373669624329</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8808962106704712</v>
+        <v>0.8870209455490112</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6502006649971008</v>
+        <v>0.6248253583908081</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0936048850417137</v>
+        <v>0.0995488166809082</v>
       </c>
       <c r="K5" t="n">
-        <v>167.5131456851959</v>
+        <v>167.8742668628693</v>
       </c>
       <c r="L5" t="n">
-        <v>3.017603635787964</v>
+        <v>2.934201955795288</v>
       </c>
       <c r="M5" t="n">
-        <v>11.65580773353577</v>
+        <v>12.23190951347351</v>
       </c>
       <c r="N5" t="n">
-        <v>19.01870894432068</v>
+        <v>19.26807808876038</v>
       </c>
       <c r="O5" t="n">
-        <v>0.251466969648997</v>
+        <v>0.2445168296496073</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9713173111279806</v>
+        <v>1.019325792789459</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.584892412026723</v>
+        <v>1.605673174063365</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250718-210310</t>
+          <t>20250722-035822</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3388,56 +3388,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="C6" t="n">
-        <v>84.89679551124573</v>
+        <v>271.8460490703583</v>
       </c>
       <c r="D6" t="n">
         <v>8.539999961853027</v>
       </c>
       <c r="E6" t="n">
-        <v>0.314804189480268</v>
+        <v>0.3166989408322234</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8819471001625061</v>
+        <v>0.9143891334533693</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8510732054710388</v>
+        <v>0.8822611570358276</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8508644104003906</v>
+        <v>0.8818768262863159</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7169907093048096</v>
+        <v>0.7435722351074219</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09393429756164549</v>
+        <v>0.1008938923478126</v>
       </c>
       <c r="K6" t="n">
-        <v>167.6987321376801</v>
+        <v>173.8808081150055</v>
       </c>
       <c r="L6" t="n">
-        <v>2.888361215591431</v>
+        <v>2.655838012695312</v>
       </c>
       <c r="M6" t="n">
-        <v>11.89771747589111</v>
+        <v>12.05051064491272</v>
       </c>
       <c r="N6" t="n">
-        <v>18.80446672439575</v>
+        <v>19.00749754905701</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2406967679659525</v>
+        <v>0.221319834391276</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9914764563242594</v>
+        <v>1.004209220409393</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.567038893699646</v>
+        <v>1.583958129088084</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250718-211002</t>
+          <t>20250722-040659</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -3675,56 +3675,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>159</v>
       </c>
       <c r="C2" t="n">
-        <v>90.84266138076782</v>
+        <v>274.4948525428772</v>
       </c>
       <c r="D2" t="n">
         <v>7.130000114440918</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1828777297418944</v>
+        <v>0.1833984515389556</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7809159755706787</v>
+        <v>0.8942980170249939</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7362121939659119</v>
+        <v>0.8800550103187561</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7354651689529419</v>
+        <v>0.8802934885025024</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6510187983512878</v>
+        <v>0.8522116541862488</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0669395104050636</v>
+        <v>0.06960463523864741</v>
       </c>
       <c r="K2" t="n">
-        <v>32.00518774986267</v>
+        <v>37.23878216743469</v>
       </c>
       <c r="L2" t="n">
-        <v>2.348804712295532</v>
+        <v>2.604402303695679</v>
       </c>
       <c r="M2" t="n">
-        <v>8.979927778244019</v>
+        <v>9.237403869628906</v>
       </c>
       <c r="N2" t="n">
-        <v>11.23652982711792</v>
+        <v>11.21477937698364</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1957337260246276</v>
+        <v>0.2170335253079732</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7483273148536682</v>
+        <v>0.7697836558024088</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.93637748559316</v>
+        <v>0.9345649480819702</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250719-132056</t>
+          <t>20250722-210446</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3796,56 +3796,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>69.11720705032349</v>
+        <v>341.1679358482361</v>
       </c>
       <c r="D3" t="n">
         <v>7.130000114440918</v>
       </c>
       <c r="E3" t="n">
-        <v>0.18323925215947</v>
+        <v>0.1827714774177302</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7243491411209106</v>
+        <v>0.8944936990737915</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6519601345062256</v>
+        <v>0.8835248947143555</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6503967642784119</v>
+        <v>0.8839021921157837</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5093042254447937</v>
+        <v>0.8858770132064819</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0686705112457275</v>
+        <v>0.06963022798299789</v>
       </c>
       <c r="K3" t="n">
-        <v>36.89620161056519</v>
+        <v>37.43187141418457</v>
       </c>
       <c r="L3" t="n">
-        <v>2.459386587142944</v>
+        <v>2.386841535568237</v>
       </c>
       <c r="M3" t="n">
-        <v>9.021799564361572</v>
+        <v>9.325448751449583</v>
       </c>
       <c r="N3" t="n">
-        <v>11.261155128479</v>
+        <v>11.11597609519958</v>
       </c>
       <c r="O3" t="n">
-        <v>0.204948882261912</v>
+        <v>0.1989034612973531</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7518166303634644</v>
+        <v>0.7771207292874655</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.938429594039917</v>
+        <v>0.926331341266632</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250719-132436</t>
+          <t>20250722-211130</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3917,56 +3917,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>154</v>
       </c>
       <c r="C4" t="n">
-        <v>68.78782081604004</v>
+        <v>264.2520608901977</v>
       </c>
       <c r="D4" t="n">
         <v>7.130000114440918</v>
       </c>
       <c r="E4" t="n">
-        <v>0.182879293827634</v>
+        <v>0.1835278109103054</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7238684892654419</v>
+        <v>0.8925288915634155</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6339197754859924</v>
+        <v>0.849295973777771</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6323339939117432</v>
+        <v>0.8489384651184082</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5208148956298828</v>
+        <v>0.8271651268005371</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0701947212219238</v>
+        <v>0.0673716887831687</v>
       </c>
       <c r="K4" t="n">
-        <v>36.74715828895569</v>
+        <v>31.39796924591064</v>
       </c>
       <c r="L4" t="n">
-        <v>2.635044574737549</v>
+        <v>2.413893222808838</v>
       </c>
       <c r="M4" t="n">
-        <v>9.213802099227903</v>
+        <v>9.766491889953612</v>
       </c>
       <c r="N4" t="n">
-        <v>11.57372999191284</v>
+        <v>12.545086145401</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2195870478947957</v>
+        <v>0.2011577685674031</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7678168416023254</v>
+        <v>0.8138743241628011</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9644774993260702</v>
+        <v>1.045423845450084</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250719-132753</t>
+          <t>20250722-211921</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4038,56 +4038,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
+        <v>199</v>
       </c>
       <c r="C5" t="n">
-        <v>69.54836535453796</v>
+        <v>341.3575859069824</v>
       </c>
       <c r="D5" t="n">
         <v>7.130000114440918</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1829555764010077</v>
+        <v>0.1826746064664131</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7530513405799866</v>
+        <v>0.89582359790802</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6367878913879395</v>
+        <v>0.8856927752494812</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6357095837593079</v>
+        <v>0.8857747316360474</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5665007829666138</v>
+        <v>0.8732470870018005</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0680538788437843</v>
+        <v>0.06727346032857889</v>
       </c>
       <c r="K5" t="n">
-        <v>36.98244023323059</v>
+        <v>37.08485436439514</v>
       </c>
       <c r="L5" t="n">
-        <v>2.459142446517944</v>
+        <v>2.458726167678833</v>
       </c>
       <c r="M5" t="n">
-        <v>9.323043823242188</v>
+        <v>9.365671634674072</v>
       </c>
       <c r="N5" t="n">
-        <v>11.21340012550354</v>
+        <v>11.43857145309448</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2049285372098287</v>
+        <v>0.2048938473065694</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7769203186035156</v>
+        <v>0.7804726362228394</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9344500104586284</v>
+        <v>0.9532142877578736</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250719-133111</t>
+          <t>20250722-212530</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4159,56 +4159,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>199</v>
       </c>
       <c r="C6" t="n">
-        <v>125.2582366466522</v>
+        <v>340.8254525661469</v>
       </c>
       <c r="D6" t="n">
         <v>7.130000114440918</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1825007517700609</v>
+        <v>0.1819488817273672</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8500016927719116</v>
+        <v>0.8932545185089111</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8027631044387817</v>
+        <v>0.8855632543563843</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8020639419555664</v>
+        <v>0.886316180229187</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7430918216705322</v>
+        <v>0.8683255910873413</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0673023089766502</v>
+        <v>0.0749744549393653</v>
       </c>
       <c r="K6" t="n">
-        <v>36.38558173179626</v>
+        <v>31.3920476436615</v>
       </c>
       <c r="L6" t="n">
-        <v>2.399601459503174</v>
+        <v>2.402316808700561</v>
       </c>
       <c r="M6" t="n">
-        <v>9.01856255531311</v>
+        <v>9.544602155685425</v>
       </c>
       <c r="N6" t="n">
-        <v>11.52878141403198</v>
+        <v>11.38846564292908</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1999667882919311</v>
+        <v>0.2001930673917134</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7515468796094259</v>
+        <v>0.7953835129737854</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9607317845026652</v>
+        <v>0.9490388035774232</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250719-133429</t>
+          <t>20250722-213320</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4446,56 +4446,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="C2" t="n">
-        <v>59.24077439308167</v>
+        <v>279.126503944397</v>
       </c>
       <c r="D2" t="n">
-        <v>4.21999979019165</v>
+        <v>4.210000038146973</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1118148423922367</v>
+        <v>0.1119387704673124</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7681484818458557</v>
+        <v>0.8898842334747314</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7512894868850708</v>
+        <v>0.8713288307189941</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7502082586288452</v>
+        <v>0.8714239597320557</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7369145750999451</v>
+        <v>0.87422776222229</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0497600249946117</v>
+        <v>0.0458385162055492</v>
       </c>
       <c r="K2" t="n">
-        <v>18.96874928474426</v>
+        <v>24.61283230781555</v>
       </c>
       <c r="L2" t="n">
-        <v>2.097837924957275</v>
+        <v>1.851269483566284</v>
       </c>
       <c r="M2" t="n">
-        <v>8.119319200515747</v>
+        <v>8.436598062515259</v>
       </c>
       <c r="N2" t="n">
-        <v>8.736038446426392</v>
+        <v>8.782293796539307</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1748198270797729</v>
+        <v>0.154272456963857</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6766099333763123</v>
+        <v>0.7030498385429382</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.728003203868866</v>
+        <v>0.7318578163782755</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250719-194832</t>
+          <t>20250723-043412</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4567,56 +4567,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>55.85191965103149</v>
+        <v>277.4149913787842</v>
       </c>
       <c r="D3" t="n">
-        <v>4.210000038146973</v>
+        <v>4.21999979019165</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1117729132896975</v>
+        <v>0.1125104003515674</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7514011859893799</v>
+        <v>0.8997436165809631</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7132983803749084</v>
+        <v>0.8875040411949158</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7112311124801636</v>
+        <v>0.8877658843994141</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6838502883911133</v>
+        <v>0.8874659538269043</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0430121421813964</v>
+        <v>0.0477079562842845</v>
       </c>
       <c r="K3" t="n">
-        <v>19.12200570106506</v>
+        <v>19.27699017524719</v>
       </c>
       <c r="L3" t="n">
-        <v>2.206352233886719</v>
+        <v>1.808266162872314</v>
       </c>
       <c r="M3" t="n">
-        <v>7.993302345275879</v>
+        <v>8.817384481430054</v>
       </c>
       <c r="N3" t="n">
-        <v>8.797682523727417</v>
+        <v>9.230767965316772</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1838626861572265</v>
+        <v>0.1506888469060262</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6661085287729899</v>
+        <v>0.7347820401191711</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.733140210310618</v>
+        <v>0.7692306637763977</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250719-195114</t>
+          <t>20250723-044035</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4688,56 +4688,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="C4" t="n">
-        <v>59.81967973709106</v>
+        <v>276.1759355068207</v>
       </c>
       <c r="D4" t="n">
         <v>4.21999979019165</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1111697720793576</v>
+        <v>0.1120164310887231</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7511184811592102</v>
+        <v>0.8925849199295044</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7183569073677063</v>
+        <v>0.8721989393234253</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7162857055664062</v>
+        <v>0.8722037076950073</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7217757701873779</v>
+        <v>0.8645178079605103</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04284493252635</v>
+        <v>0.0428309440612793</v>
       </c>
       <c r="K4" t="n">
-        <v>19.35852742195129</v>
+        <v>19.13998818397522</v>
       </c>
       <c r="L4" t="n">
-        <v>2.178910732269287</v>
+        <v>1.780080080032349</v>
       </c>
       <c r="M4" t="n">
-        <v>7.79816722869873</v>
+        <v>8.187046766281128</v>
       </c>
       <c r="N4" t="n">
-        <v>9.175762414932253</v>
+        <v>8.932053327560425</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1815758943557739</v>
+        <v>0.1483400066693624</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6498472690582275</v>
+        <v>0.682253897190094</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7646468679110209</v>
+        <v>0.744337777296702</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250719-195353</t>
+          <t>20250723-044659</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4809,56 +4809,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="C5" t="n">
-        <v>60.10404920578003</v>
+        <v>277.7388498783112</v>
       </c>
       <c r="D5" t="n">
         <v>4.210000038146973</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1107305786930597</v>
+        <v>0.1112273941986524</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7617562413215637</v>
+        <v>0.8902050256729126</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7353466749191284</v>
+        <v>0.8776947259902954</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7347970008850098</v>
+        <v>0.8787301778793335</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7206995487213135</v>
+        <v>0.8757151365280151</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0521230697631835</v>
+        <v>0.0437413863837718</v>
       </c>
       <c r="K5" t="n">
-        <v>24.73036885261536</v>
+        <v>19.12789034843445</v>
       </c>
       <c r="L5" t="n">
-        <v>2.168038606643677</v>
+        <v>1.712865352630615</v>
       </c>
       <c r="M5" t="n">
-        <v>7.887514352798462</v>
+        <v>7.938342809677124</v>
       </c>
       <c r="N5" t="n">
-        <v>8.831470727920532</v>
+        <v>8.9511399269104</v>
       </c>
       <c r="O5" t="n">
-        <v>0.180669883886973</v>
+        <v>0.1427387793858846</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6572928627332052</v>
+        <v>0.6615285674730936</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7359558939933777</v>
+        <v>0.7459283272425333</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250719-195637</t>
+          <t>20250723-045319</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4930,56 +4930,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="C6" t="n">
-        <v>59.64116168022156</v>
+        <v>277.7706038951874</v>
       </c>
       <c r="D6" t="n">
         <v>4.21999979019165</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1116938491662342</v>
+        <v>0.1118817786176</v>
       </c>
       <c r="F6" t="n">
-        <v>0.746173620223999</v>
+        <v>0.8952585458755493</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6793244481086731</v>
+        <v>0.8812369108200073</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6782305836677551</v>
+        <v>0.8809704184532166</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6679348349571228</v>
+        <v>0.879368782043457</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0446321181952953</v>
+        <v>0.0427647419273853</v>
       </c>
       <c r="K6" t="n">
-        <v>18.79312014579773</v>
+        <v>19.33892917633057</v>
       </c>
       <c r="L6" t="n">
-        <v>2.021730661392212</v>
+        <v>1.81603217124939</v>
       </c>
       <c r="M6" t="n">
-        <v>7.796379327774048</v>
+        <v>8.135734796524048</v>
       </c>
       <c r="N6" t="n">
-        <v>8.811955451965332</v>
+        <v>8.934448957443237</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1684775551160176</v>
+        <v>0.1513360142707824</v>
       </c>
       <c r="P6" t="n">
-        <v>0.649698277314504</v>
+        <v>0.6779778997103373</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.734329620997111</v>
+        <v>0.7445374131202698</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250719-195920</t>
+          <t>20250723-045940</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5217,56 +5217,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>199</v>
       </c>
       <c r="C2" t="n">
-        <v>53.89302229881287</v>
+        <v>266.7209150791168</v>
       </c>
       <c r="D2" t="n">
         <v>2.809999942779541</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1023805098314034</v>
+        <v>0.1021027669085928</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7516684532165527</v>
+        <v>0.8861501216888428</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6885724067687988</v>
+        <v>0.8769717216491699</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6868134737014771</v>
+        <v>0.8777788281440735</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6873812675476074</v>
+        <v>0.8775249719619751</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0362508296966552</v>
+        <v>0.0440353564918041</v>
       </c>
       <c r="K2" t="n">
-        <v>23.18435645103454</v>
+        <v>24.04195952415466</v>
       </c>
       <c r="L2" t="n">
-        <v>1.974176168441772</v>
+        <v>1.698066234588623</v>
       </c>
       <c r="M2" t="n">
-        <v>8.444583892822266</v>
+        <v>7.869767904281616</v>
       </c>
       <c r="N2" t="n">
-        <v>9.512596607208252</v>
+        <v>9.617883920669556</v>
       </c>
       <c r="O2" t="n">
-        <v>0.164514680703481</v>
+        <v>0.1415055195490519</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7037153244018555</v>
+        <v>0.655813992023468</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.792716383934021</v>
+        <v>0.801490326722463</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250720-001118</t>
+          <t>20250723-100644</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5338,56 +5338,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>56.31847667694092</v>
+        <v>266.4008736610413</v>
       </c>
       <c r="D3" t="n">
         <v>2.809999942779541</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1005713154490177</v>
+        <v>0.1030532849868337</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7357177734375</v>
+        <v>0.8888245820999146</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7032692432403564</v>
+        <v>0.8738598823547363</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7044950723648071</v>
+        <v>0.8741155862808228</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6435073018074036</v>
+        <v>0.8726091384887695</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0376570224761962</v>
+        <v>0.0371832847595214</v>
       </c>
       <c r="K3" t="n">
-        <v>23.57219123840332</v>
+        <v>23.29406332969665</v>
       </c>
       <c r="L3" t="n">
-        <v>1.734437942504883</v>
+        <v>1.669889450073242</v>
       </c>
       <c r="M3" t="n">
-        <v>8.343053102493286</v>
+        <v>7.863600015640259</v>
       </c>
       <c r="N3" t="n">
-        <v>9.455350875854492</v>
+        <v>9.167787075042725</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1445364952087402</v>
+        <v>0.1391574541727701</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6952544252077738</v>
+        <v>0.6553000013033549</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7879459063212076</v>
+        <v>0.7639822562535604</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250720-001355</t>
+          <t>20250723-101255</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5459,56 +5459,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="C4" t="n">
-        <v>55.25925087928772</v>
+        <v>259.2440857887268</v>
       </c>
       <c r="D4" t="n">
         <v>2.809999942779541</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1012061956601264</v>
+        <v>0.1031080667097963</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7418212890625</v>
+        <v>0.8910282850265503</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6979333162307739</v>
+        <v>0.8660720586776733</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6966990232467651</v>
+        <v>0.8664802312850952</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6961019039154053</v>
+        <v>0.8632940053939819</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0380349159240722</v>
+        <v>0.0398127250373363</v>
       </c>
       <c r="K4" t="n">
-        <v>23.7610125541687</v>
+        <v>22.97562193870544</v>
       </c>
       <c r="L4" t="n">
-        <v>1.697547435760498</v>
+        <v>1.713006734848022</v>
       </c>
       <c r="M4" t="n">
-        <v>8.333701848983765</v>
+        <v>8.015422821044922</v>
       </c>
       <c r="N4" t="n">
-        <v>9.802629947662354</v>
+        <v>9.381561517715454</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1414622863133748</v>
+        <v>0.1427505612373352</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6944751540819804</v>
+        <v>0.6679519017537435</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8168858289718628</v>
+        <v>0.7817967931429545</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250720-001635</t>
+          <t>20250723-101904</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5580,56 +5580,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="C5" t="n">
-        <v>56.64010643959045</v>
+        <v>259.8125987052917</v>
       </c>
       <c r="D5" t="n">
         <v>2.809999942779541</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1026273853121659</v>
+        <v>0.1028102826533005</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7426595687866211</v>
+        <v>0.8877965211868286</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7420934438705444</v>
+        <v>0.872536838054657</v>
       </c>
       <c r="H5" t="n">
-        <v>0.742026686668396</v>
+        <v>0.8730394244194031</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7433436512947083</v>
+        <v>0.8730615377426147</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0515377521514892</v>
+        <v>0.0345483608543872</v>
       </c>
       <c r="K5" t="n">
-        <v>23.80171418190002</v>
+        <v>24.03073239326477</v>
       </c>
       <c r="L5" t="n">
-        <v>1.757633447647095</v>
+        <v>1.665667295455933</v>
       </c>
       <c r="M5" t="n">
-        <v>8.330028295516968</v>
+        <v>7.94441294670105</v>
       </c>
       <c r="N5" t="n">
-        <v>10.04406976699829</v>
+        <v>9.437903881072998</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1464694539705912</v>
+        <v>0.138805607954661</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6941690246264139</v>
+        <v>0.6620344122250875</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8370058139165243</v>
+        <v>0.7864919900894165</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250720-001914</t>
+          <t>20250723-102506</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5701,56 +5701,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="C6" t="n">
-        <v>54.78823280334473</v>
+        <v>262.255119562149</v>
       </c>
       <c r="D6" t="n">
-        <v>2.809999942779541</v>
+        <v>2.829999923706055</v>
       </c>
       <c r="E6" t="n">
-        <v>0.100705923178257</v>
+        <v>0.1042419239204732</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7479730248451233</v>
+        <v>0.8875765800476074</v>
       </c>
       <c r="G6" t="n">
-        <v>0.697075366973877</v>
+        <v>0.8587599992752075</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6970201730728149</v>
+        <v>0.8593764305114746</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6878833770751953</v>
+        <v>0.8616219758987427</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0358688831329345</v>
+        <v>0.0346307754516601</v>
       </c>
       <c r="K6" t="n">
-        <v>23.9289939403534</v>
+        <v>23.57464361190796</v>
       </c>
       <c r="L6" t="n">
-        <v>1.646290063858032</v>
+        <v>1.606992483139038</v>
       </c>
       <c r="M6" t="n">
-        <v>8.574026823043823</v>
+        <v>8.037488222122192</v>
       </c>
       <c r="N6" t="n">
-        <v>9.460681438446043</v>
+        <v>9.57146692276001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.137190838654836</v>
+        <v>0.1339160402615865</v>
       </c>
       <c r="P6" t="n">
-        <v>0.714502235253652</v>
+        <v>0.6697906851768494</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7883901198705038</v>
+        <v>0.7976222435633341</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250720-002155</t>
+          <t>20250723-103110</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
